--- a/HGA/MASTER GAMBAR.xlsx
+++ b/HGA/MASTER GAMBAR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD HGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5CA4E0-C8CA-42FD-994D-5CC9A8E01F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E936E89-239F-4164-94EE-D252F57DDE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3ADC970B-AF40-422A-B8D9-698DD6F80022}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
   <si>
     <t>Tipe Motor</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>https://github.com/suwandakurnia/gambar-aksesoris/blob/main/VARIO%20160/eCatalog%20Honda%20Collection%20update%20Apr%2025_page-0078.jpg?raw=true</t>
+  </si>
+  <si>
+    <t>2025 ADV 160</t>
+  </si>
+  <si>
+    <t>2025 VARIO 125</t>
   </si>
 </sst>
 </file>
@@ -205,12 +211,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -225,8 +237,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -245,7 +258,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2CF655CC-DB9D-4F68-8848-80A6D7A123D4}" name="MASTER_GAMBAR" displayName="MASTER_GAMBAR" ref="A1:B53" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2CF655CC-DB9D-4F68-8848-80A6D7A123D4}" name="MASTER_GAMBAR" displayName="MASTER_GAMBAR" ref="A1:B55" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E28232FD-98C6-47A9-9CF0-6586A8D0937F}" name="Tipe Motor"/>
     <tableColumn id="2" xr3:uid="{81C0F3E3-6113-4540-9D59-9FA742ED74E8}" name="Url"/>
@@ -571,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61716D0B-BA11-4E2A-9264-78BF1D4FB5E3}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -1000,6 +1013,22 @@
       </c>
       <c r="B53" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
